--- a/backend/src/data/pharmacy.xlsx
+++ b/backend/src/data/pharmacy.xlsx
@@ -5,13 +5,14 @@
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
     <sheet sheetId="1" name="Pharmacy" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Dispensed" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="18">
   <si>
     <t>Medicine ID</t>
   </si>
@@ -50,6 +51,21 @@
   </si>
   <si>
     <t>31/5/2026, 3:54:32 pm</t>
+  </si>
+  <si>
+    <t>Dispense ID</t>
+  </si>
+  <si>
+    <t>Patient OP</t>
+  </si>
+  <si>
+    <t>Quantity Dispensed</t>
+  </si>
+  <si>
+    <t>Total Amount</t>
+  </si>
+  <si>
+    <t>Dispensed Date</t>
   </si>
 </sst>
 </file>
@@ -492,4 +508,40 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="4" width="20" customWidth="1"/>
+    <col min="5" max="5" width="15" customWidth="1"/>
+    <col min="6" max="6" width="25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
 </file>